--- a/kb023_products.xlsx
+++ b/kb023_products.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d251688e3d9c1650/Cursor/KB023/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{DB1DD3B8-2F1F-4F39-B6D4-0D3D770DD1AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E464BEE-66B6-45C4-9285-E78B0DD21615}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{DB1DD3B8-2F1F-4F39-B6D4-0D3D770DD1AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66617B9E-59D8-42CF-BD54-429E11F30508}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{761E7EB1-A17D-4169-B242-B30F569385B2}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{761E7EB1-A17D-4169-B242-B30F569385B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Insurance products" sheetId="4" r:id="rId1"/>
@@ -66,346 +66,351 @@
     <t>건강/상해보험</t>
   </si>
   <si>
+    <t>KB 7년의약속 플러스 평생종신보험 무배당(해약환급금 일부지급형)(간편심사형)</t>
+  </si>
+  <si>
+    <t>KB 약속플러스 종신보험 무배당(해약환급금 일부지급형)(일반심사형)</t>
+  </si>
+  <si>
+    <t>KB 라이프 파트너 종신보험 무배당(해약환급금 일부지급형)(일반심사형)</t>
+  </si>
+  <si>
+    <t>KB 약속플러스 종신보험 무배당(해약환급금 일부지급형)(간편심사형)</t>
+  </si>
+  <si>
+    <t>KB 경영인정기보험Ⅲ 무배당(해약환급금 일부지급형)(간편심사형)</t>
+  </si>
+  <si>
+    <t>KB 종신보험 무배당(간편심사형)</t>
+  </si>
+  <si>
+    <t>KB 착한정기보험II 무배당</t>
+  </si>
+  <si>
+    <t>KB 더블업 역모기지 종신보험 무배당(해약환급금 미지급형)(일반심사형)</t>
+  </si>
+  <si>
+    <t>KB 역모기지 일시납종신보험 무배당(일반심사형)</t>
+  </si>
+  <si>
+    <t>KB 경영인정기보험Ⅲ 무배당(해약환급금 일부지급형)(일반심사형)</t>
+  </si>
+  <si>
+    <t>KB 정기보험 무배당</t>
+  </si>
+  <si>
+    <t>KB 7년의약속 플러스 평생종신보험 무배당(해약환급금 일부지급형)(일반심사형)</t>
+  </si>
+  <si>
+    <t>KB 라이프 파트너 종신보험 무배당(해약환급금 일부지급형)(간편심사형)</t>
+  </si>
+  <si>
+    <t>KB 달러평생보장보험 무배당(일반심사형)</t>
+  </si>
+  <si>
+    <t>KB Trust 라이프 파트너 종신보험 무배당(해약환급금 일부지급형)(일반심사형)</t>
+  </si>
+  <si>
+    <t>KB 라이프 역모기지 종신보험 무배당(해약환급금 일부지급형)(간편심사형)</t>
+  </si>
+  <si>
+    <t>KB 역모기지 체증종신보험 무배당(해약환급금 일부지급형)(일반심사형)</t>
+  </si>
+  <si>
+    <t>KB 라이프 역모기지 종신보험 무배당(해약환급금 일부지급형)(일반심사형)</t>
+  </si>
+  <si>
+    <t>KB 역모기지 체증종신보험 무배당(해약환급금 일부지급형)(간편심사형)</t>
+  </si>
+  <si>
+    <t>KB 역모기지 일시납종신보험 무배당(간편심사형)</t>
+  </si>
+  <si>
+    <t>KB 소득보장보험 무배당</t>
+  </si>
+  <si>
+    <t>KB 달러평생보장보험 무배당(간편심사형)</t>
+  </si>
+  <si>
+    <t>KB 넥스트 레벨업 연금보험 무배당(미보증형)</t>
+  </si>
+  <si>
+    <t>KB 트리플 레벨업 연금보험 무배당(보증형)</t>
+  </si>
+  <si>
+    <t>KB 트리플 레벨업 연금보험 무배당(미보증형)</t>
+  </si>
+  <si>
+    <t>KB 넥스트 레벨업 연금보험 무배당(보증형)</t>
+  </si>
+  <si>
+    <t>KB 하이파이브평생연금보험 무배당</t>
+  </si>
+  <si>
+    <t>KB 5.10.5 딱좋은 플러스 건강보험 무배당(건강고지형)</t>
+  </si>
+  <si>
+    <t>KB 3.10.5 딱좋은 초경증 건강보험 무배당(간편심사형)(납입면제형)</t>
+  </si>
+  <si>
+    <t>KB 딱좋은 e-건강보험 무배당(갱신형)(간편심사형(355))(해약환급금 미지급형)</t>
+  </si>
+  <si>
+    <t>KB 딱좋은 e-건강보험 무배당(갱신형)(일반심사형)(해약환급금 미지급형)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KB 지켜주는 대중교통안심보험 무배당</t>
+  </si>
+  <si>
+    <t>KB 지켜주는 교통안심보험 무배당</t>
+  </si>
+  <si>
+    <t>KB 착한암보험 무배당</t>
+  </si>
+  <si>
+    <t>KB 5.10.5 딱좋은 플러스 건강보험 무배당(건강고지형)(납입면제형)</t>
+  </si>
+  <si>
+    <t>KB 5.10.5 딱좋은 플러스 건강보험 무배당(건강고지형)(해약환급금 미지급형)</t>
+  </si>
+  <si>
+    <t>KB 평생소득변액연금보험 무배당</t>
+  </si>
+  <si>
+    <t>KB VIP 변액연금보험 무배당(보증형)</t>
+  </si>
+  <si>
+    <t>KB VIP 변액연금보험 무배당(미보증형)</t>
+  </si>
+  <si>
+    <t>KB 달러평생소득변액연금보험 무배당(월납)(노후소득미보증형)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KB 달러평생소득변액연금보험 무배당(노후소득미보증형)</t>
+  </si>
+  <si>
+    <t>KB 평생소득변액연금보험 무배당(노후소득미보증형)</t>
+  </si>
+  <si>
+    <t>KB 달러평생소득변액연금보험 무배당</t>
+  </si>
+  <si>
+    <t>KB 달러평생소득변액연금보험 무배당(월납)</t>
+  </si>
+  <si>
+    <t>kbinsure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동차/운전자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KB자동차보험</t>
+  </si>
+  <si>
+    <t>마일리지 할인 특약</t>
+  </si>
+  <si>
+    <t>첨단안전장치 장착특약</t>
+  </si>
+  <si>
+    <t>커넥티드카 안전운전 할인 특약</t>
+  </si>
+  <si>
+    <t>커넥티드카 할인특약</t>
+  </si>
+  <si>
+    <t>이동통신단말장치 안전운전</t>
+  </si>
+  <si>
+    <t>대중교통 이용 할인 특약</t>
+  </si>
+  <si>
+    <t>자녀할인특약</t>
+  </si>
+  <si>
+    <t>KB The건강한 치아보험</t>
+  </si>
+  <si>
+    <t>자동차보험(개인)</t>
+  </si>
+  <si>
+    <t>자동차보험(법인)</t>
+  </si>
+  <si>
+    <t>자동차보험(영업용)</t>
+  </si>
+  <si>
+    <t>이륜차보험(개인)</t>
+  </si>
+  <si>
+    <t>이륜차보험(법인)</t>
+  </si>
+  <si>
+    <t>운전자보험(3년이상)</t>
+  </si>
+  <si>
+    <t>오토바이운전자보험</t>
+  </si>
+  <si>
+    <t>운전자+자전거보험(1~3년)</t>
+  </si>
+  <si>
+    <t>주택화재보험</t>
+  </si>
+  <si>
+    <t>해외여행보험</t>
+  </si>
+  <si>
+    <t>해외장기체류(유학/출장)보험</t>
+  </si>
+  <si>
+    <t>건강맞춤보장보험(종합플랜)</t>
+  </si>
+  <si>
+    <t>금쪽같은 펫보험</t>
+  </si>
+  <si>
+    <t>간편건강보험</t>
+  </si>
+  <si>
+    <t>실손의료비보험</t>
+  </si>
+  <si>
+    <t>간편가입실손의료비보험</t>
+  </si>
+  <si>
+    <t>자녀보험(태아포함)</t>
+  </si>
+  <si>
+    <t>치아&amp;뇌 보험</t>
+  </si>
+  <si>
+    <t>내맘대로암보험</t>
+  </si>
+  <si>
+    <t>골프보험</t>
+  </si>
+  <si>
+    <t>하루운전자보험(1~7일)</t>
+  </si>
+  <si>
+    <t>사장님종합보험</t>
+  </si>
+  <si>
+    <t>소상공인 풍수해·지진재해보험</t>
+  </si>
+  <si>
+    <t>다이렉트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자녀/건강/상해</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KB 9회주는 암보험Plus</t>
+  </si>
+  <si>
+    <t>KB Yes!365 건강보험(연만기)</t>
+  </si>
+  <si>
+    <t>KB Yes!365 건강보험(세만기)</t>
+  </si>
+  <si>
+    <t>KB금쪽같은자녀보험Plus</t>
+  </si>
+  <si>
+    <t>KB 손보 실손의료비보장보험</t>
+  </si>
+  <si>
+    <t>KB손보간편가입실손의료비보장보험</t>
+  </si>
+  <si>
+    <t>KB 5.10.10 플러스 건강보험</t>
+  </si>
+  <si>
+    <t>KB멀티플러스연금보험</t>
+  </si>
+  <si>
+    <t>KB빅플러스저축보험</t>
+  </si>
+  <si>
+    <t>연금/저축</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KB 손보 노후실손의료비보장보험</t>
+  </si>
+  <si>
+    <t>노후/간병</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KB홈앤비즈케어종합보험</t>
+  </si>
+  <si>
+    <t>KB주택화재보험</t>
+  </si>
+  <si>
+    <t>주택·온실 풍수해·지진재해보험Ⅰ</t>
+  </si>
+  <si>
+    <t>화재</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>펫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KB 금쪽같은 펫보험(강아지)</t>
+  </si>
+  <si>
+    <t>KB 금쪽같은 펫보험(고양이)</t>
+  </si>
+  <si>
+    <t>BIZ보험</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기업번창종합보험</t>
+  </si>
+  <si>
+    <t>적하보험</t>
+  </si>
+  <si>
+    <t>PL보험</t>
+  </si>
+  <si>
+    <t>보험사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상품종류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>KB 더블업 역모기지 종신보험 무배당(해약환급금 미지급형)(간편심사형)</t>
-  </si>
-  <si>
-    <t>KB 7년의약속 플러스 평생종신보험 무배당(해약환급금 일부지급형)(간편심사형)</t>
-  </si>
-  <si>
-    <t>KB 약속플러스 종신보험 무배당(해약환급금 일부지급형)(일반심사형)</t>
-  </si>
-  <si>
-    <t>KB 라이프 파트너 종신보험 무배당(해약환급금 일부지급형)(일반심사형)</t>
-  </si>
-  <si>
-    <t>KB 약속플러스 종신보험 무배당(해약환급금 일부지급형)(간편심사형)</t>
-  </si>
-  <si>
-    <t>KB 경영인정기보험Ⅲ 무배당(해약환급금 일부지급형)(간편심사형)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>KB 종신보험 무배당(일반심사형)</t>
-  </si>
-  <si>
-    <t>KB 종신보험 무배당(간편심사형)</t>
-  </si>
-  <si>
-    <t>KB 착한정기보험II 무배당</t>
-  </si>
-  <si>
-    <t>KB 더블업 역모기지 종신보험 무배당(해약환급금 미지급형)(일반심사형)</t>
-  </si>
-  <si>
-    <t>KB 역모기지 일시납종신보험 무배당(일반심사형)</t>
-  </si>
-  <si>
-    <t>KB 경영인정기보험Ⅲ 무배당(해약환급금 일부지급형)(일반심사형)</t>
-  </si>
-  <si>
-    <t>KB 정기보험 무배당</t>
-  </si>
-  <si>
-    <t>KB 7년의약속 플러스 평생종신보험 무배당(해약환급금 일부지급형)(일반심사형)</t>
-  </si>
-  <si>
-    <t>KB 라이프 파트너 종신보험 무배당(해약환급금 일부지급형)(간편심사형)</t>
-  </si>
-  <si>
-    <t>KB 달러평생보장보험 무배당(일반심사형)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>KB Trust 라이프 파트너 종신보험 무배당(해약환급금 일부지급형)(간편심사형)</t>
-  </si>
-  <si>
-    <t>KB Trust 라이프 파트너 종신보험 무배당(해약환급금 일부지급형)(일반심사형)</t>
-  </si>
-  <si>
-    <t>KB 라이프 역모기지 종신보험 무배당(해약환급금 일부지급형)(간편심사형)</t>
-  </si>
-  <si>
-    <t>KB 역모기지 체증종신보험 무배당(해약환급금 일부지급형)(일반심사형)</t>
-  </si>
-  <si>
-    <t>KB 라이프 역모기지 종신보험 무배당(해약환급금 일부지급형)(일반심사형)</t>
-  </si>
-  <si>
-    <t>KB 역모기지 체증종신보험 무배당(해약환급금 일부지급형)(간편심사형)</t>
-  </si>
-  <si>
-    <t>KB 역모기지 일시납종신보험 무배당(간편심사형)</t>
-  </si>
-  <si>
-    <t>KB 소득보장보험 무배당</t>
-  </si>
-  <si>
-    <t>KB 달러평생보장보험 무배당(간편심사형)</t>
-  </si>
-  <si>
-    <t>KB 넥스트 레벨업 연금보험 무배당(미보증형)</t>
-  </si>
-  <si>
-    <t>KB 트리플 레벨업 연금보험 무배당(보증형)</t>
-  </si>
-  <si>
-    <t>KB 트리플 레벨업 연금보험 무배당(미보증형)</t>
-  </si>
-  <si>
-    <t>KB 넥스트 레벨업 연금보험 무배당(보증형)</t>
-  </si>
-  <si>
-    <t>KB 하이파이브평생연금보험 무배당</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>KB 5.10.5 딱좋은 플러스 건강보험 무배당(건강고지형)(해약환급금 미지급형)(납입면제형)</t>
-  </si>
-  <si>
-    <t>KB 5.10.5 딱좋은 플러스 건강보험 무배당(건강고지형)</t>
-  </si>
-  <si>
-    <t>KB 3.10.5 딱좋은 초경증 건강보험 무배당(간편심사형)(납입면제형)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>KB 3.10.5 딱좋은 초경증 건강보험 무배당(간편심사형)(해약환급금 미지급형)(납입면제형)</t>
-  </si>
-  <si>
-    <t>KB 딱좋은 e-건강보험 무배당(갱신형)(간편심사형(355))(해약환급금 미지급형)</t>
-  </si>
-  <si>
-    <t>KB 딱좋은 e-건강보험 무배당(갱신형)(일반심사형)(해약환급금 미지급형)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KB 지켜주는 대중교통안심보험 무배당</t>
-  </si>
-  <si>
-    <t>KB 지켜주는 교통안심보험 무배당</t>
-  </si>
-  <si>
-    <t>KB 착한암보험 무배당</t>
-  </si>
-  <si>
-    <t>KB 5.10.5 딱좋은 플러스 건강보험 무배당(건강고지형)(납입면제형)</t>
-  </si>
-  <si>
-    <t>KB 5.10.5 딱좋은 플러스 건강보험 무배당(건강고지형)(해약환급금 미지급형)</t>
-  </si>
-  <si>
-    <t>KB 평생소득변액연금보험 무배당</t>
-  </si>
-  <si>
-    <t>KB VIP 변액연금보험 무배당(보증형)</t>
-  </si>
-  <si>
-    <t>KB VIP 변액연금보험 무배당(미보증형)</t>
-  </si>
-  <si>
-    <t>KB 달러평생소득변액연금보험 무배당(월납)(노후소득미보증형)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KB 달러평생소득변액연금보험 무배당(노후소득미보증형)</t>
-  </si>
-  <si>
-    <t>KB 평생소득변액연금보험 무배당(노후소득미보증형)</t>
-  </si>
-  <si>
-    <t>KB 달러평생소득변액연금보험 무배당</t>
-  </si>
-  <si>
-    <t>KB 달러평생소득변액연금보험 무배당(월납)</t>
-  </si>
-  <si>
-    <t>kbinsure</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>자동차/운전자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KB자동차보험</t>
-  </si>
-  <si>
-    <t>마일리지 할인 특약</t>
-  </si>
-  <si>
-    <t>첨단안전장치 장착특약</t>
-  </si>
-  <si>
-    <t>커넥티드카 안전운전 할인 특약</t>
-  </si>
-  <si>
-    <t>커넥티드카 할인특약</t>
-  </si>
-  <si>
-    <t>이동통신단말장치 안전운전</t>
-  </si>
-  <si>
-    <t>대중교통 이용 할인 특약</t>
-  </si>
-  <si>
-    <t>자녀할인특약</t>
-  </si>
-  <si>
-    <t>KB The건강한 치아보험</t>
-  </si>
-  <si>
-    <t>자동차보험(개인)</t>
-  </si>
-  <si>
-    <t>자동차보험(법인)</t>
-  </si>
-  <si>
-    <t>자동차보험(영업용)</t>
-  </si>
-  <si>
-    <t>이륜차보험(개인)</t>
-  </si>
-  <si>
-    <t>이륜차보험(법인)</t>
-  </si>
-  <si>
-    <t>운전자보험(3년이상)</t>
-  </si>
-  <si>
-    <t>오토바이운전자보험</t>
-  </si>
-  <si>
-    <t>운전자+자전거보험(1~3년)</t>
-  </si>
-  <si>
-    <t>주택화재보험</t>
-  </si>
-  <si>
-    <t>해외여행보험</t>
-  </si>
-  <si>
-    <t>해외장기체류(유학/출장)보험</t>
-  </si>
-  <si>
-    <t>건강맞춤보장보험(종합플랜)</t>
-  </si>
-  <si>
-    <t>금쪽같은 펫보험</t>
-  </si>
-  <si>
-    <t>간편건강보험</t>
-  </si>
-  <si>
-    <t>실손의료비보험</t>
-  </si>
-  <si>
-    <t>간편가입실손의료비보험</t>
-  </si>
-  <si>
-    <t>자녀보험(태아포함)</t>
-  </si>
-  <si>
-    <t>치아&amp;뇌 보험</t>
-  </si>
-  <si>
-    <t>내맘대로암보험</t>
-  </si>
-  <si>
-    <t>골프보험</t>
-  </si>
-  <si>
-    <t>하루운전자보험(1~7일)</t>
-  </si>
-  <si>
-    <t>사장님종합보험</t>
-  </si>
-  <si>
-    <t>소상공인 풍수해·지진재해보험</t>
-  </si>
-  <si>
-    <t>다이렉트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>자녀/건강/상해</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KB 9회주는 암보험Plus</t>
-  </si>
-  <si>
-    <t>KB Yes!365 건강보험(연만기)</t>
-  </si>
-  <si>
-    <t>KB Yes!365 건강보험(세만기)</t>
-  </si>
-  <si>
-    <t>KB금쪽같은자녀보험Plus</t>
-  </si>
-  <si>
-    <t>KB 손보 실손의료비보장보험</t>
-  </si>
-  <si>
-    <t>KB손보간편가입실손의료비보장보험</t>
-  </si>
-  <si>
-    <t>KB 5.10.10 플러스 건강보험</t>
-  </si>
-  <si>
-    <t>KB멀티플러스연금보험</t>
-  </si>
-  <si>
-    <t>KB빅플러스저축보험</t>
-  </si>
-  <si>
-    <t>연금/저축</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KB 손보 노후실손의료비보장보험</t>
-  </si>
-  <si>
-    <t>노후/간병</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KB홈앤비즈케어종합보험</t>
-  </si>
-  <si>
-    <t>KB주택화재보험</t>
-  </si>
-  <si>
-    <t>주택·온실 풍수해·지진재해보험Ⅰ</t>
-  </si>
-  <si>
-    <t>화재</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>펫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KB 금쪽같은 펫보험(강아지)</t>
-  </si>
-  <si>
-    <t>KB 금쪽같은 펫보험(고양이)</t>
-  </si>
-  <si>
-    <t>BIZ보험</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>기업번창종합보험</t>
-  </si>
-  <si>
-    <t>적하보험</t>
-  </si>
-  <si>
-    <t>PL보험</t>
-  </si>
-  <si>
-    <t>보험사</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>상품종류</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -489,6 +494,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -818,10 +827,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -835,7 +844,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -846,7 +855,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -857,7 +866,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -868,7 +877,7 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -879,7 +888,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -890,7 +899,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -901,7 +910,7 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -912,7 +921,7 @@
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -923,7 +932,7 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -934,7 +943,7 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -945,7 +954,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -956,7 +965,7 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -967,7 +976,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -978,7 +987,7 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -989,7 +998,7 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -1000,7 +1009,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -1011,7 +1020,7 @@
         <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -1022,7 +1031,7 @@
         <v>5</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -1033,7 +1042,7 @@
         <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -1044,7 +1053,7 @@
         <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -1055,7 +1064,7 @@
         <v>5</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -1066,7 +1075,7 @@
         <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -1077,7 +1086,7 @@
         <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -1088,7 +1097,7 @@
         <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -1099,7 +1108,7 @@
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -1110,7 +1119,7 @@
         <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -1121,7 +1130,7 @@
         <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -1132,7 +1141,7 @@
         <v>3</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -1143,7 +1152,7 @@
         <v>3</v>
       </c>
       <c r="C30" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -1154,7 +1163,7 @@
         <v>3</v>
       </c>
       <c r="C31" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -1165,7 +1174,7 @@
         <v>6</v>
       </c>
       <c r="C32" t="s">
-        <v>37</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -1176,7 +1185,7 @@
         <v>6</v>
       </c>
       <c r="C33" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -1187,7 +1196,7 @@
         <v>6</v>
       </c>
       <c r="C34" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -1198,7 +1207,7 @@
         <v>6</v>
       </c>
       <c r="C35" t="s">
-        <v>40</v>
+        <v>116</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -1209,7 +1218,7 @@
         <v>6</v>
       </c>
       <c r="C36" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -1220,7 +1229,7 @@
         <v>6</v>
       </c>
       <c r="C37" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -1231,7 +1240,7 @@
         <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -1242,7 +1251,7 @@
         <v>6</v>
       </c>
       <c r="C39" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -1253,7 +1262,7 @@
         <v>6</v>
       </c>
       <c r="C40" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
@@ -1264,7 +1273,7 @@
         <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
@@ -1275,7 +1284,7 @@
         <v>6</v>
       </c>
       <c r="C42" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
@@ -1286,7 +1295,7 @@
         <v>4</v>
       </c>
       <c r="C43" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -1297,7 +1306,7 @@
         <v>4</v>
       </c>
       <c r="C44" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
@@ -1308,7 +1317,7 @@
         <v>4</v>
       </c>
       <c r="C45" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
@@ -1319,7 +1328,7 @@
         <v>4</v>
       </c>
       <c r="C46" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
@@ -1330,7 +1339,7 @@
         <v>4</v>
       </c>
       <c r="C47" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
@@ -1341,7 +1350,7 @@
         <v>4</v>
       </c>
       <c r="C48" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -1352,7 +1361,7 @@
         <v>4</v>
       </c>
       <c r="C49" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
@@ -1363,356 +1372,356 @@
         <v>4</v>
       </c>
       <c r="C50" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B51" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C51" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C52" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C53" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>51</v>
+      </c>
+      <c r="B54" t="s">
+        <v>52</v>
+      </c>
+      <c r="C54" t="s">
         <v>56</v>
-      </c>
-      <c r="B54" t="s">
-        <v>57</v>
-      </c>
-      <c r="C54" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B55" t="s">
+        <v>52</v>
+      </c>
+      <c r="C55" t="s">
         <v>57</v>
-      </c>
-      <c r="C55" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B56" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C56" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C57" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B58" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C58" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B59" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C59" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B60" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C60" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B61" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C61" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B62" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C62" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B63" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C63" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B64" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C64" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B65" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C65" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B66" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C66" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B67" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C67" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B68" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C68" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B69" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C69" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B70" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C70" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B71" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C71" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B72" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C72" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B73" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C73" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B74" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C74" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B75" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C75" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B76" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C76" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B77" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C77" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B78" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C78" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B79" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C79" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B80" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C80" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B81" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B82" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C82" t="s">
         <v>2</v>
@@ -1720,211 +1729,211 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B83" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C83" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B84" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C84" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B85" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C85" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B86" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C86" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B87" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C87" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B88" t="s">
+        <v>86</v>
+      </c>
+      <c r="C88" t="s">
         <v>91</v>
-      </c>
-      <c r="C88" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B89" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C89" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B90" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C90" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B91" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C91" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B92" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C92" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B93" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C93" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B94" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C94" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B95" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C95" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B96" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C96" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B97" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C97" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B98" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C98" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B99" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C99" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B100" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C100" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C101" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
